--- a/Tiempos Rendimiento.xlsx
+++ b/Tiempos Rendimiento.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de Uso" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">GUIA DE USO — Ejemplo de Registro de Tiempos de Ejecucion</t>
   </si>
@@ -220,7 +220,31 @@
     <t xml:space="preserve">Si / No</t>
   </si>
   <si>
+    <t xml:space="preserve">Gráfica plana, el tiempo apenas cambia al aumentar n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misma tendencia plana, ambos hacen n operaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se mantiene cerca de cero incluso en n=30</t>
+  </si>
+  <si>
     <t>O(2^n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La curva explota a partir de n=25, crecimiento exponencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El tiempo sube proporcional al tamaño del arreglo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misma tendencia lineal ascendente que el iterativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parábola: 10x más datos = ~100x más tiempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curva casi idéntica al iterativo, misma parábola</t>
   </si>
   <si>
     <t xml:space="preserve">Guia para interpretar tus graficas:</t>
@@ -257,7 +281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -385,12 +409,17 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="9.500000"/>
+      <color indexed="63"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="9.000000"/>
       <color indexed="63"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,8 +492,14 @@
         <bgColor rgb="FFFFF3E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -535,11 +570,39 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD6D6D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD6D6D6"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD6D6D6"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -661,19 +724,28 @@
     <xf fontId="20" fillId="9" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="23" fillId="13" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="23" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="23" fillId="7" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="23" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="24" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="23" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="24" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="7" fillId="12" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="23" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="24" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5660,7 +5732,9 @@
       <c r="F4" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="40"/>
+      <c r="G4" s="40" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="5" ht="21.75" customHeight="1">
       <c r="B5" s="41" t="s">
@@ -5678,7 +5752,9 @@
       <c r="F5" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="40"/>
+      <c r="G5" s="43" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" ht="21.75" customHeight="1">
       <c r="B6" s="36" t="s">
@@ -5696,7 +5772,9 @@
       <c r="F6" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="40"/>
+      <c r="G6" s="44" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="7" ht="21.75" customHeight="1">
       <c r="B7" s="41" t="s">
@@ -5709,12 +5787,14 @@
         <v>55</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F7" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="40"/>
+      <c r="G7" s="43" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
       <c r="B8" s="36" t="s">
@@ -5732,7 +5812,9 @@
       <c r="F8" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="40"/>
+      <c r="G8" s="44" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" ht="21.75" customHeight="1">
       <c r="B9" s="41" t="s">
@@ -5750,7 +5832,9 @@
       <c r="F9" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="40"/>
+      <c r="G9" s="43" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
       <c r="B10" s="36" t="s">
@@ -5768,7 +5852,9 @@
       <c r="F10" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="40"/>
+      <c r="G10" s="45" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" ht="21.75" customHeight="1">
       <c r="B11" s="41" t="s">
@@ -5786,12 +5872,14 @@
       <c r="F11" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="40"/>
+      <c r="G11" s="40" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" ht="7.5" customHeight="1"/>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="43" t="s">
-        <v>58</v>
+      <c r="B15" s="46" t="s">
+        <v>66</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -5801,10 +5889,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>60</v>
+        <v>67</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>68</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -5813,10 +5901,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="B17" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>62</v>
+        <v>69</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>70</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -5825,10 +5913,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>64</v>
+        <v>71</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>72</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -5836,11 +5924,11 @@
       <c r="G18" s="4"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="B19" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>66</v>
+      <c r="B19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
